--- a/Delivery Sheet.xlsx
+++ b/Delivery Sheet.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/animesh/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1BD3852-E8C1-934A-9604-6F994FE39DA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A9F3E4A-D915-D143-B803-B135597E5CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-1340" windowWidth="38400" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="$125 " sheetId="1" r:id="rId1"/>
-    <sheet name="$125" sheetId="2" r:id="rId2"/>
-    <sheet name="$150" sheetId="3" r:id="rId3"/>
-    <sheet name="$175" sheetId="4" r:id="rId4"/>
+    <sheet name="$150 " sheetId="1" r:id="rId1"/>
+    <sheet name="$150" sheetId="2" r:id="rId2"/>
+    <sheet name="$175" sheetId="3" r:id="rId3"/>
+    <sheet name="$200" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'$125'!$A$1:$C$118</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'$150'!$A$1:$C$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'$150'!$A$1:$C$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'$175'!$A$1:$C$57</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
